--- a/pipeline_output/KARNATAK_2W_H&M.xlsx
+++ b/pipeline_output/KARNATAK_2W_H&M.xlsx
@@ -736,12 +736,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1732,12 +1732,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4349,12 +4349,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5472,12 +5472,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5960,12 +5960,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -7999,12 +7999,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -8116,12 +8116,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -8233,12 +8233,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -9209,12 +9209,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -9911,12 +9911,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -10090,7 +10090,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -10262,12 +10262,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -10496,12 +10496,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -10558,7 +10558,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -10730,12 +10730,12 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -10857,12 +10857,12 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -10984,12 +10984,12 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -11355,12 +11355,12 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -11589,12 +11589,12 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -12204,12 +12204,12 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -12448,12 +12448,12 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -12575,12 +12575,12 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -12702,12 +12702,12 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -12819,12 +12819,12 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -12946,12 +12946,12 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -13190,12 +13190,12 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -13444,12 +13444,12 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -13688,12 +13688,12 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -13815,12 +13815,12 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -13942,12 +13942,12 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -14069,12 +14069,12 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -14186,12 +14186,12 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -14303,12 +14303,12 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -14420,12 +14420,12 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -14537,12 +14537,12 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -14654,12 +14654,12 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -14781,12 +14781,12 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -14908,12 +14908,12 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -15035,12 +15035,12 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -15279,12 +15279,12 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -15406,12 +15406,12 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -15533,12 +15533,12 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -15650,12 +15650,12 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -15777,12 +15777,12 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="AQ125" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>500</t>
         </is>
       </c>
     </row>
@@ -15904,12 +15904,12 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -16021,12 +16021,12 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -16148,12 +16148,12 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -16337,7 +16337,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -16392,12 +16392,12 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -16581,7 +16581,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -16646,12 +16646,12 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -16708,7 +16708,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -16773,12 +16773,12 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -16900,12 +16900,12 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -17017,12 +17017,12 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -17079,7 +17079,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -17134,12 +17134,12 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -17196,7 +17196,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -17251,12 +17251,12 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -17313,7 +17313,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -17368,12 +17368,12 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN138" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -17485,12 +17485,12 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
@@ -17547,7 +17547,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -17612,12 +17612,12 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -17674,7 +17674,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -17739,12 +17739,12 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -17801,7 +17801,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -17866,12 +17866,12 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -17928,7 +17928,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -17993,12 +17993,12 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -18055,7 +18055,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -18110,12 +18110,12 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN144" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -18172,7 +18172,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -18237,12 +18237,12 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
@@ -18299,7 +18299,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -18481,12 +18481,12 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
@@ -18543,7 +18543,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -18608,12 +18608,12 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -18670,7 +18670,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -18735,12 +18735,12 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
@@ -18797,7 +18797,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -18979,12 +18979,12 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -19041,7 +19041,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>KARNATAKA</t>
+          <t>KARNATAKA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -19106,12 +19106,12 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -19233,12 +19233,12 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -19360,12 +19360,12 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -19487,12 +19487,12 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -19614,12 +19614,12 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -19741,12 +19741,12 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -19868,12 +19868,12 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN158" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -19995,12 +19995,12 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN159" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -20239,12 +20239,12 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN161" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -20356,12 +20356,12 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -20473,12 +20473,12 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN163" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
@@ -20590,12 +20590,12 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN164" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
@@ -20707,12 +20707,12 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN165" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
@@ -20824,12 +20824,12 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN166" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
@@ -20941,12 +20941,12 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -21058,12 +21058,12 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN168" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
@@ -21175,12 +21175,12 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN169" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -21292,12 +21292,12 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -21409,12 +21409,12 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN171" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -21526,12 +21526,12 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -21643,12 +21643,12 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -21760,12 +21760,12 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
@@ -21877,12 +21877,12 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
@@ -21994,12 +21994,12 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
